--- a/Tables/Table 2.xlsx
+++ b/Tables/Table 2.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csole\Dropbox\01tesis\07Articulos\3. Especies nuevas (alba)\00PAPER\Tablas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csole\Dropbox\01tesis\08Articulos\2. Convergencias (alba)\00PAPER\Tablas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E17B42D-1400-45DD-BE3F-575A6537C6F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7B8740-27DE-4D2F-A762-216EEA1623FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="2985" windowWidth="21600" windowHeight="10680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="660" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="l2JGW0c9Tb+qz/+WYi60zkPOeTOBjaDHt1+beQ7vZOs="/>
     </ext>
@@ -51,9 +54,6 @@
     <t>COI</t>
   </si>
   <si>
-    <t>5′ GGTCAACAAATCATAAAGATGGGG 3′</t>
-  </si>
-  <si>
     <t>Metazoa-universal</t>
   </si>
   <si>
@@ -66,51 +66,49 @@
     <t>5′ TAAACTTCAGGGTGACCAAAAAATCA 3′</t>
   </si>
   <si>
-    <t xml:space="preserve">ArCOIR </t>
+    <t>González-Miguéns et al., 2022a</t>
   </si>
   <si>
-    <t>5' CCACYNGGAWTGCRTAARATACC 3'</t>
+    <t>5' CCACTTGAATGHGMADYWATACTAC 3'</t>
+  </si>
+  <si>
+    <t>This work</t>
+  </si>
+  <si>
+    <t>5′ GGTCAACAAATCATAAAGATATTGG 3′</t>
+  </si>
+  <si>
+    <t>ArCOIR</t>
+  </si>
+  <si>
+    <t>5' CCACYNGAATGWGCTARAATACC 3'</t>
   </si>
   <si>
     <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-      </rPr>
       <t>Arcella</t>
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
       </rPr>
       <t>-specific</t>
     </r>
   </si>
   <si>
-    <t>González-Miguéns et al., 2022a</t>
+    <t>LONR</t>
   </si>
   <si>
-    <t xml:space="preserve">LONR </t>
-  </si>
-  <si>
-    <t>5' CCACTTGAATGHGMADYWATACTAC 3'</t>
-  </si>
-  <si>
-    <t>Longithecina-specific</t>
-  </si>
-  <si>
-    <t>This work</t>
+    <t>Arcellinida-specific</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -124,23 +122,73 @@
     </font>
     <font>
       <i/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -149,13 +197,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -372,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z1000"/>
+  <dimension ref="A1:Z994"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -384,23 +450,23 @@
     <col min="7" max="26" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:26" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1"/>
@@ -425,23 +491,23 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4">
+        <v>700</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1">
-        <v>700</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -465,23 +531,23 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="D3" s="5">
         <v>700</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
@@ -505,23 +571,23 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
+      <c r="A4" s="3" t="s">
+        <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
+      <c r="C4" s="4" t="s">
+        <v>17</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="4">
         <v>350</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
+      <c r="E4" s="6" t="s">
+        <v>18</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
+      <c r="F4" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
@@ -545,23 +611,23 @@
       <c r="Z4" s="1"/>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
+      <c r="A5" s="3" t="s">
+        <v>19</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="5">
         <v>350</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>19</v>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
+      <c r="F5" s="8" t="s">
+        <v>14</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -836,7 +902,7 @@
       <c r="Y14" s="1"/>
       <c r="Z14" s="1"/>
     </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -864,7 +930,7 @@
       <c r="Y15" s="1"/>
       <c r="Z15" s="1"/>
     </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -892,7 +958,7 @@
       <c r="Y16" s="1"/>
       <c r="Z16" s="1"/>
     </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -920,7 +986,7 @@
       <c r="Y17" s="1"/>
       <c r="Z17" s="1"/>
     </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -948,7 +1014,7 @@
       <c r="Y18" s="1"/>
       <c r="Z18" s="1"/>
     </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -976,7 +1042,7 @@
       <c r="Y19" s="1"/>
       <c r="Z19" s="1"/>
     </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -28276,174 +28342,6 @@
       <c r="Y994" s="1"/>
       <c r="Z994" s="1"/>
     </row>
-    <row r="995" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A995" s="1"/>
-      <c r="B995" s="1"/>
-      <c r="C995" s="1"/>
-      <c r="D995" s="1"/>
-      <c r="E995" s="1"/>
-      <c r="F995" s="1"/>
-      <c r="G995" s="1"/>
-      <c r="H995" s="1"/>
-      <c r="I995" s="1"/>
-      <c r="J995" s="1"/>
-      <c r="K995" s="1"/>
-      <c r="L995" s="1"/>
-      <c r="M995" s="1"/>
-      <c r="N995" s="1"/>
-      <c r="O995" s="1"/>
-      <c r="P995" s="1"/>
-      <c r="Q995" s="1"/>
-      <c r="R995" s="1"/>
-      <c r="S995" s="1"/>
-      <c r="T995" s="1"/>
-      <c r="U995" s="1"/>
-      <c r="V995" s="1"/>
-      <c r="W995" s="1"/>
-      <c r="X995" s="1"/>
-      <c r="Y995" s="1"/>
-      <c r="Z995" s="1"/>
-    </row>
-    <row r="996" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A996" s="1"/>
-      <c r="B996" s="1"/>
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
-      <c r="E996" s="1"/>
-      <c r="F996" s="1"/>
-      <c r="G996" s="1"/>
-      <c r="H996" s="1"/>
-      <c r="I996" s="1"/>
-      <c r="J996" s="1"/>
-      <c r="K996" s="1"/>
-      <c r="L996" s="1"/>
-      <c r="M996" s="1"/>
-      <c r="N996" s="1"/>
-      <c r="O996" s="1"/>
-      <c r="P996" s="1"/>
-      <c r="Q996" s="1"/>
-      <c r="R996" s="1"/>
-      <c r="S996" s="1"/>
-      <c r="T996" s="1"/>
-      <c r="U996" s="1"/>
-      <c r="V996" s="1"/>
-      <c r="W996" s="1"/>
-      <c r="X996" s="1"/>
-      <c r="Y996" s="1"/>
-      <c r="Z996" s="1"/>
-    </row>
-    <row r="997" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
-      <c r="H997" s="1"/>
-      <c r="I997" s="1"/>
-      <c r="J997" s="1"/>
-      <c r="K997" s="1"/>
-      <c r="L997" s="1"/>
-      <c r="M997" s="1"/>
-      <c r="N997" s="1"/>
-      <c r="O997" s="1"/>
-      <c r="P997" s="1"/>
-      <c r="Q997" s="1"/>
-      <c r="R997" s="1"/>
-      <c r="S997" s="1"/>
-      <c r="T997" s="1"/>
-      <c r="U997" s="1"/>
-      <c r="V997" s="1"/>
-      <c r="W997" s="1"/>
-      <c r="X997" s="1"/>
-      <c r="Y997" s="1"/>
-      <c r="Z997" s="1"/>
-    </row>
-    <row r="998" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A998" s="1"/>
-      <c r="B998" s="1"/>
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="1"/>
-      <c r="G998" s="1"/>
-      <c r="H998" s="1"/>
-      <c r="I998" s="1"/>
-      <c r="J998" s="1"/>
-      <c r="K998" s="1"/>
-      <c r="L998" s="1"/>
-      <c r="M998" s="1"/>
-      <c r="N998" s="1"/>
-      <c r="O998" s="1"/>
-      <c r="P998" s="1"/>
-      <c r="Q998" s="1"/>
-      <c r="R998" s="1"/>
-      <c r="S998" s="1"/>
-      <c r="T998" s="1"/>
-      <c r="U998" s="1"/>
-      <c r="V998" s="1"/>
-      <c r="W998" s="1"/>
-      <c r="X998" s="1"/>
-      <c r="Y998" s="1"/>
-      <c r="Z998" s="1"/>
-    </row>
-    <row r="999" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A999" s="1"/>
-      <c r="B999" s="1"/>
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
-      <c r="H999" s="1"/>
-      <c r="I999" s="1"/>
-      <c r="J999" s="1"/>
-      <c r="K999" s="1"/>
-      <c r="L999" s="1"/>
-      <c r="M999" s="1"/>
-      <c r="N999" s="1"/>
-      <c r="O999" s="1"/>
-      <c r="P999" s="1"/>
-      <c r="Q999" s="1"/>
-      <c r="R999" s="1"/>
-      <c r="S999" s="1"/>
-      <c r="T999" s="1"/>
-      <c r="U999" s="1"/>
-      <c r="V999" s="1"/>
-      <c r="W999" s="1"/>
-      <c r="X999" s="1"/>
-      <c r="Y999" s="1"/>
-      <c r="Z999" s="1"/>
-    </row>
-    <row r="1000" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="1"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
-      <c r="I1000" s="1"/>
-      <c r="J1000" s="1"/>
-      <c r="K1000" s="1"/>
-      <c r="L1000" s="1"/>
-      <c r="M1000" s="1"/>
-      <c r="N1000" s="1"/>
-      <c r="O1000" s="1"/>
-      <c r="P1000" s="1"/>
-      <c r="Q1000" s="1"/>
-      <c r="R1000" s="1"/>
-      <c r="S1000" s="1"/>
-      <c r="T1000" s="1"/>
-      <c r="U1000" s="1"/>
-      <c r="V1000" s="1"/>
-      <c r="W1000" s="1"/>
-      <c r="X1000" s="1"/>
-      <c r="Y1000" s="1"/>
-      <c r="Z1000" s="1"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
